--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medication.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Medication</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Medication|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -371,7 +371,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -514,7 +514,7 @@
     <t>薬品の種類を規定するコード化された概念</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS|1.1.0a</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -560,7 +560,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -595,7 +595,7 @@
     <t>もし、Medication ResourceがMedicationRequest Resourceから参照された場合は、これはオーダされた剤型である。Medication ResourceがMedicationDispense Resourceから参照された場合は、払い出された剤型である。MedicationAdministration ResourceからMedication Resourceが参照されていれば、投与された剤型である。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationFormMERIT9_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationFormMERIT9_VS|1.1.0a</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -612,7 +612,7 @@
     <t>Medication.amount</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_Amount}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_Amount|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -691,7 +691,7 @@
     <t>drugNo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_Ingredient_DrugNo}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_Ingredient_DrugNo|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -798,7 +798,7 @@
     <t>strengthType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_IngredientStrength_StrengthType}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_IngredientStrength_StrengthType|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -811,7 +811,7 @@
     <t>Medication.ingredient.strength.numerator</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1219,7 +1219,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="91.2890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="99.28125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1234,7 +1234,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="79.203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.48046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medication.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Medication|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Medication</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -371,7 +371,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -514,7 +514,7 @@
     <t>薬品の種類を規定するコード化された概念</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -560,7 +560,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -595,7 +595,7 @@
     <t>もし、Medication ResourceがMedicationRequest Resourceから参照された場合は、これはオーダされた剤型である。Medication ResourceがMedicationDispense Resourceから参照された場合は、払い出された剤型である。MedicationAdministration ResourceからMedication Resourceが参照されていれば、投与された剤型である。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationFormMERIT9_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationFormMERIT9_VS</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -612,7 +612,7 @@
     <t>Medication.amount</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_Amount|1.3.0-dev}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_Amount}
 </t>
   </si>
   <si>
@@ -691,7 +691,7 @@
     <t>drugNo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_Ingredient_DrugNo|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_Ingredient_DrugNo}
 </t>
   </si>
   <si>
@@ -798,7 +798,7 @@
     <t>strengthType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_IngredientStrength_StrengthType|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_IngredientStrength_StrengthType}
 </t>
   </si>
   <si>
@@ -811,7 +811,7 @@
     <t>Medication.ingredient.strength.numerator</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationQuantity}
 </t>
   </si>
   <si>
@@ -1219,7 +1219,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="99.28125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="91.2890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1234,7 +1234,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="79.203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.48046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
